--- a/tame_output/ON/bt/strategyON_20231228.xlsx
+++ b/tame_output/ON/bt/strategyON_20231228.xlsx
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487812</v>
+        <v>3.146053372487813</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823383</v>
+        <v>3.146265744823384</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524824</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068704</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714846</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097101</v>
+        <v>3.163432091097102</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762261</v>
+        <v>3.169279212762262</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -43491,10 +43491,10 @@
         <v>3.133773427784875</v>
       </c>
       <c r="D1825" t="n">
-        <v>0.1059660314761421</v>
+        <v>0.1060508593364863</v>
       </c>
       <c r="E1825" t="n">
-        <v>3.175803416061585</v>
+        <v>3.175837347205723</v>
       </c>
       <c r="F1825" t="n">
         <v>1.720735441343577</v>

--- a/tame_output/ON/bt/strategyON_20231228.xlsx
+++ b/tame_output/ON/bt/strategyON_20231228.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487813</v>
+        <v>3.146053372487812</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823384</v>
+        <v>3.146265744823383</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524824</v>
+        <v>3.157777201524823</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068704</v>
+        <v>3.157294380068703</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714846</v>
+        <v>3.147014107714845</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097102</v>
+        <v>3.163432091097101</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762262</v>
+        <v>3.169279212762261</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.18551435596348</v>
+        <v>3.185514355963479</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
@@ -43491,10 +43491,10 @@
         <v>3.133773427784875</v>
       </c>
       <c r="D1825" t="n">
-        <v>0.1060508593364863</v>
+        <v>0.1065038553125497</v>
       </c>
       <c r="E1825" t="n">
-        <v>3.175837347205723</v>
+        <v>3.176018545596148</v>
       </c>
       <c r="F1825" t="n">
         <v>1.720735441343577</v>

--- a/tame_output/ON/bt/strategyON_20231228.xlsx
+++ b/tame_output/ON/bt/strategyON_20231228.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>92.7%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85.5%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>485.2%</t>
+          <t>479.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-162.7%</t>
+          <t>-161.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-131.8%</t>
+          <t>-142.2%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.967739618787158</v>
+        <v>-4.067483184268049</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.484352948197105</v>
+        <v>1.444455522004749</v>
       </c>
       <c r="F1790" t="n">
         <v>-0.1440976815076501</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.972748733848742</v>
+        <v>-4.072492299329633</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.482866382001331</v>
+        <v>1.442968955808975</v>
       </c>
       <c r="F1791" t="n">
         <v>-0.1450922590661848</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.976454290485557</v>
+        <v>-4.076197855966448</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.48061188458697</v>
+        <v>1.440714458394614</v>
       </c>
       <c r="F1792" t="n">
         <v>-0.1469619343238197</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.975221965128191</v>
+        <v>-4.074965530609082</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.481524666792236</v>
+        <v>1.44162724059988</v>
       </c>
       <c r="F1793" t="n">
         <v>-0.1463315579517822</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.964893968112339</v>
+        <v>-4.064637533593229</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.48978577376279</v>
+        <v>1.449888347570434</v>
       </c>
       <c r="F1794" t="n">
         <v>-0.13600356093593</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.964777632964783</v>
+        <v>-4.064521198445673</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.496352968023649</v>
+        <v>1.456455541831293</v>
       </c>
       <c r="F1795" t="n">
         <v>-0.1358872257883743</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.966623042541651</v>
+        <v>-4.066366608022541</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.492588774638291</v>
+        <v>1.452691348445935</v>
       </c>
       <c r="F1796" t="n">
         <v>-0.1358872257883743</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.965124610016552</v>
+        <v>-4.064868175497442</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.493126435509464</v>
+        <v>1.453229009317108</v>
       </c>
       <c r="F1797" t="n">
         <v>-0.1343887932632754</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.973188862209286</v>
+        <v>-4.072932427690175</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.491178712575682</v>
+        <v>1.451281286383326</v>
       </c>
       <c r="F1798" t="n">
         <v>-0.1424530454560092</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.974518829670498</v>
+        <v>-4.074262395151388</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.490646725591197</v>
+        <v>1.450749299398841</v>
       </c>
       <c r="F1799" t="n">
         <v>-0.1424530454560092</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.746654146936987</v>
+        <v>-3.846397712417877</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.584009071791764</v>
+        <v>1.544111645599407</v>
       </c>
       <c r="F1800" t="n">
         <v>-0.1424530454560092</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-3.498552583069769</v>
+        <v>-3.59829614855066</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.690784293683743</v>
+        <v>1.650886867491386</v>
       </c>
       <c r="F1801" t="n">
         <v>-0.1424530454560092</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-3.201714183676439</v>
+        <v>-3.30145774915733</v>
       </c>
       <c r="E1802" t="n">
-        <v>1.810942664414532</v>
+        <v>1.771045238222176</v>
       </c>
       <c r="F1802" t="n">
         <v>-0.02759855697488151</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.898074626851003</v>
+        <v>-2.997818192331894</v>
       </c>
       <c r="E1803" t="n">
-        <v>1.934075561610393</v>
+        <v>1.894178135418037</v>
       </c>
       <c r="F1803" t="n">
         <v>-0.02759855697488151</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-2.609054020410294</v>
+        <v>-2.708797585891185</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.045623225636134</v>
+        <v>2.005725799443778</v>
       </c>
       <c r="F1804" t="n">
         <v>-0.02759855697488151</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-2.324334093146397</v>
+        <v>-2.424077658627288</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.164731335885711</v>
+        <v>2.124833909693355</v>
       </c>
       <c r="F1805" t="n">
         <v>0.2571213702890157</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-2.040572423654857</v>
+        <v>-2.140315989135748</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.283548166856133</v>
+        <v>2.243650740663778</v>
       </c>
       <c r="F1806" t="n">
         <v>0.2571213702890157</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.778924029262216</v>
+        <v>-1.878667594743107</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.381450112059823</v>
+        <v>2.341552685867467</v>
       </c>
       <c r="F1807" t="n">
         <v>0.5187697646816563</v>
@@ -43100,10 +43100,10 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-1.464757591122884</v>
+        <v>-1.564501156603775</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.504580362331669</v>
+        <v>2.464682936139313</v>
       </c>
       <c r="F1808" t="n">
         <v>0.8329362028209887</v>
@@ -43123,10 +43123,10 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-1.342245887017112</v>
+        <v>-1.441989452498002</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.571999427600717</v>
+        <v>2.532102001408361</v>
       </c>
       <c r="F1809" t="n">
         <v>0.9554479069267611</v>
@@ -43146,10 +43146,10 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-1.180857353090383</v>
+        <v>-1.280600918571274</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.646370965226887</v>
+        <v>2.606473539034531</v>
       </c>
       <c r="F1810" t="n">
         <v>1.116836440853489</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-1.001111161941877</v>
+        <v>-1.100854727422768</v>
       </c>
       <c r="E1811" t="n">
-        <v>2.731797053738221</v>
+        <v>2.691899627545865</v>
       </c>
       <c r="F1811" t="n">
         <v>1.116836440853489</v>
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.8423102354706542</v>
+        <v>-0.9420538009515449</v>
       </c>
       <c r="E1812" t="n">
-        <v>2.801904804577976</v>
+        <v>2.76200737838562</v>
       </c>
       <c r="F1812" t="n">
         <v>1.116836440853489</v>
@@ -43215,10 +43215,10 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.7495217771652773</v>
+        <v>-0.849265342646168</v>
       </c>
       <c r="E1813" t="n">
-        <v>2.827930936334833</v>
+        <v>2.788033510142477</v>
       </c>
       <c r="F1813" t="n">
         <v>1.209624899158866</v>
@@ -43238,10 +43238,10 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>-0.6555012817944355</v>
+        <v>-0.7552448472753261</v>
       </c>
       <c r="E1814" t="n">
-        <v>2.861139631993894</v>
+        <v>2.821242205801538</v>
       </c>
       <c r="F1814" t="n">
         <v>1.21946733965185</v>
@@ -43261,10 +43261,10 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>-0.5653983138879124</v>
+        <v>-0.6651418793688031</v>
       </c>
       <c r="E1815" t="n">
-        <v>2.883160595663233</v>
+        <v>2.843263169470877</v>
       </c>
       <c r="F1815" t="n">
         <v>1.222525533939635</v>
@@ -43284,10 +43284,10 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>-0.5212691431663372</v>
+        <v>-0.6210127086472279</v>
       </c>
       <c r="E1816" t="n">
-        <v>2.918261842706992</v>
+        <v>2.878364416514636</v>
       </c>
       <c r="F1816" t="n">
         <v>1.306544706926906</v>
@@ -43307,10 +43307,10 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>-0.5114990989886424</v>
+        <v>-0.6112426644695331</v>
       </c>
       <c r="E1817" t="n">
-        <v>2.921197910762147</v>
+        <v>2.88130048456979</v>
       </c>
       <c r="F1817" t="n">
         <v>1.385903597981972</v>
@@ -43330,10 +43330,10 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>-0.4748607762206677</v>
+        <v>-0.5746043417015585</v>
       </c>
       <c r="E1818" t="n">
-        <v>2.92515596095218</v>
+        <v>2.885258534759823</v>
       </c>
       <c r="F1818" t="n">
         <v>1.385903597981972</v>
@@ -43353,10 +43353,10 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>-0.4262150977509345</v>
+        <v>-0.5259586632318252</v>
       </c>
       <c r="E1819" t="n">
-        <v>2.954531187802287</v>
+        <v>2.91463376160993</v>
       </c>
       <c r="F1819" t="n">
         <v>1.434549276451705</v>
@@ -43376,10 +43376,10 @@
         <v>3.132226628875955</v>
       </c>
       <c r="D1820" t="n">
-        <v>-0.3657351953315321</v>
+        <v>-0.4654787608124228</v>
       </c>
       <c r="E1820" t="n">
-        <v>2.985576126429595</v>
+        <v>2.945678700237239</v>
       </c>
       <c r="F1820" t="n">
         <v>1.495029178871107</v>
@@ -43399,10 +43399,10 @@
         <v>3.134450814492048</v>
       </c>
       <c r="D1821" t="n">
-        <v>-0.2831851278154152</v>
+        <v>-0.3829286932963059</v>
       </c>
       <c r="E1821" t="n">
-        <v>3.020820339052135</v>
+        <v>2.980922912859779</v>
       </c>
       <c r="F1821" t="n">
         <v>1.495029178871107</v>
@@ -43422,10 +43422,10 @@
         <v>3.121045839271831</v>
       </c>
       <c r="D1822" t="n">
-        <v>-0.2053490401201986</v>
+        <v>-0.3050926056010893</v>
       </c>
       <c r="E1822" t="n">
-        <v>3.038549798910005</v>
+        <v>2.998652372717649</v>
       </c>
       <c r="F1822" t="n">
         <v>1.573611131527232</v>
@@ -43445,10 +43445,10 @@
         <v>3.126711518797542</v>
       </c>
       <c r="D1823" t="n">
-        <v>-0.08847237450529327</v>
+        <v>-0.188215939986184</v>
       </c>
       <c r="E1823" t="n">
-        <v>3.090966144681678</v>
+        <v>3.051068718489322</v>
       </c>
       <c r="F1823" t="n">
         <v>1.656180472986857</v>
@@ -43468,10 +43468,10 @@
         <v>3.130543841755795</v>
       </c>
       <c r="D1824" t="n">
-        <v>-0.02391740614857313</v>
+        <v>-0.1236609716294638</v>
       </c>
       <c r="E1824" t="n">
-        <v>3.120620454982619</v>
+        <v>3.080723028790263</v>
       </c>
       <c r="F1824" t="n">
         <v>1.720735441343577</v>
@@ -43485,16 +43485,16 @@
         <v>45287</v>
       </c>
       <c r="B1825" t="n">
-        <v>3.122818766852275</v>
+        <v>3.162220658105229</v>
       </c>
       <c r="C1825" t="n">
         <v>3.133773427784875</v>
       </c>
       <c r="D1825" t="n">
-        <v>0.1065038553125497</v>
+        <v>0.002447381098183044</v>
       </c>
       <c r="E1825" t="n">
-        <v>3.176018545596148</v>
+        <v>3.134395955910402</v>
       </c>
       <c r="F1825" t="n">
         <v>1.720735441343577</v>

--- a/tame_output/ON/bt/strategyON_20231228.xlsx
+++ b/tame_output/ON/bt/strategyON_20231228.xlsx
@@ -42887,7 +42887,7 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
